--- a/Outputs/Recycling_Plot_Data/Repeal/05_Cumulative_Minerals_Lost_data_Repeal.xlsx
+++ b/Outputs/Recycling_Plot_Data/Repeal/05_Cumulative_Minerals_Lost_data_Repeal.xlsx
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>6.642251084369247</v>
+        <v>6.558833671689219</v>
       </c>
     </row>
     <row r="3">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>4.104616269824274</v>
+        <v>4.062261461261987</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>14.96502944888701</v>
+        <v>14.797599512151</v>
       </c>
     </row>
     <row r="5">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>157.6350118201625</v>
+        <v>155.9157147232363</v>
       </c>
     </row>
   </sheetData>
